--- a/iphones.xlsx
+++ b/iphones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\telegram_bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45DB450-7CD8-45E7-A412-48624C3AFADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511C23A9-0EC1-41A1-924C-463994A46C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10095" yWindow="0" windowWidth="10410" windowHeight="10905" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Iphone 6" sheetId="3" r:id="rId1"/>
@@ -725,9 +725,6 @@
       <c r="B3">
         <v>2450</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1125,7 +1122,7 @@
         <v>3700</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1135,9 +1132,6 @@
       <c r="B3">
         <v>2800</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1147,7 +1141,7 @@
         <v>2000</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1158,7 +1152,7 @@
         <v>1000</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1169,7 +1163,7 @@
         <v>1200</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1180,7 +1174,7 @@
         <v>2400</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1191,7 +1185,7 @@
         <v>1400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1202,7 +1196,7 @@
         <v>2300</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1213,7 +1207,7 @@
         <v>1400</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1224,7 +1218,7 @@
         <v>400</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1234,6 +1228,9 @@
       <c r="B12">
         <v>2200</v>
       </c>
+      <c r="C12">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1243,7 +1240,7 @@
         <v>1100</v>
       </c>
       <c r="C13">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1334,7 +1331,7 @@
         <v>4400</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1344,9 +1341,6 @@
       <c r="B3">
         <v>3400</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1356,7 +1350,7 @@
         <v>2500</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1367,7 +1361,7 @@
         <v>1200</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1378,7 +1372,7 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1389,7 +1383,7 @@
         <v>2500</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1400,7 +1394,7 @@
         <v>1400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1411,7 +1405,7 @@
         <v>2400</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1422,7 +1416,7 @@
         <v>1400</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1433,7 +1427,7 @@
         <v>400</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1443,6 +1437,9 @@
       <c r="B12">
         <v>2200</v>
       </c>
+      <c r="C12">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1452,7 +1449,7 @@
         <v>1100</v>
       </c>
       <c r="C13">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1543,7 +1540,7 @@
         <v>2900</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,9 +1550,6 @@
       <c r="B3">
         <v>1900</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1565,7 +1559,7 @@
         <v>2200</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1576,7 +1570,7 @@
         <v>1200</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1587,7 +1581,7 @@
         <v>1500</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1598,7 +1592,7 @@
         <v>2300</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1609,7 +1603,7 @@
         <v>1500</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1620,7 +1614,7 @@
         <v>2100</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1631,7 +1625,7 @@
         <v>1500</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1642,7 +1636,7 @@
         <v>400</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1660,6 +1654,9 @@
       <c r="B13">
         <v>2400</v>
       </c>
+      <c r="C13">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1669,7 +1666,7 @@
         <v>1300</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,7 +1757,7 @@
         <v>3800</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1770,9 +1767,6 @@
       <c r="B3">
         <v>3000</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1782,7 +1776,7 @@
         <v>2400</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1793,7 +1787,7 @@
         <v>1300</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1804,7 +1798,7 @@
         <v>1600</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1815,7 +1809,7 @@
         <v>3000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1826,7 +1820,7 @@
         <v>1600</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1837,7 +1831,7 @@
         <v>2700</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1848,7 +1842,7 @@
         <v>1600</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1859,7 +1853,7 @@
         <v>400</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1877,6 +1871,9 @@
       <c r="B13">
         <v>2500</v>
       </c>
+      <c r="C13">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1886,7 +1883,7 @@
         <v>1800</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1977,7 +1974,7 @@
         <v>5300</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1987,9 +1984,6 @@
       <c r="B3">
         <v>3500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -1999,7 +1993,7 @@
         <v>3200</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2010,7 +2004,7 @@
         <v>1300</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2021,7 +2015,7 @@
         <v>1700</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,7 +2026,7 @@
         <v>3100</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2043,7 +2037,7 @@
         <v>1600</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2054,7 +2048,7 @@
         <v>2700</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2065,7 +2059,7 @@
         <v>1600</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2076,7 +2070,7 @@
         <v>400</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2094,6 +2088,9 @@
       <c r="B13">
         <v>2500</v>
       </c>
+      <c r="C13">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2103,7 +2100,7 @@
         <v>2000</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2194,7 +2191,7 @@
         <v>4200</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2204,9 +2201,6 @@
       <c r="B3">
         <v>3500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2216,7 +2210,7 @@
         <v>3300</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2227,7 +2221,7 @@
         <v>1400</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2238,7 +2232,7 @@
         <v>1800</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2249,7 +2243,7 @@
         <v>2800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2260,7 +2254,7 @@
         <v>1800</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2271,7 +2265,7 @@
         <v>2700</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2282,7 +2276,7 @@
         <v>2000</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2293,7 +2287,7 @@
         <v>500</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2311,6 +2305,9 @@
       <c r="B13">
         <v>2700</v>
       </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2320,7 +2317,7 @@
         <v>1500</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2411,7 +2408,7 @@
         <v>5100</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2421,9 +2418,6 @@
       <c r="B3">
         <v>3500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2433,7 +2427,7 @@
         <v>3000</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2444,7 +2438,7 @@
         <v>1400</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2455,7 +2449,7 @@
         <v>1800</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2466,7 +2460,7 @@
         <v>2800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2477,7 +2471,7 @@
         <v>1800</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2488,7 +2482,7 @@
         <v>2800</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2499,7 +2493,7 @@
         <v>2000</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2510,7 +2504,7 @@
         <v>500</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2528,6 +2522,9 @@
       <c r="B13">
         <v>2700</v>
       </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2537,7 +2534,7 @@
         <v>1500</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2685,7 +2682,7 @@
         <v>5100</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,9 +2692,6 @@
       <c r="B3">
         <v>3500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2707,7 +2701,7 @@
         <v>3000</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2718,7 +2712,7 @@
         <v>1400</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2729,7 +2723,7 @@
         <v>1800</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2740,7 +2734,7 @@
         <v>3800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2751,7 +2745,7 @@
         <v>1800</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2762,7 +2756,7 @@
         <v>3500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2773,7 +2767,7 @@
         <v>2000</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2784,7 +2778,7 @@
         <v>500</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2802,6 +2796,9 @@
       <c r="B13">
         <v>2700</v>
       </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -2811,7 +2808,7 @@
         <v>1500</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2902,7 +2899,7 @@
         <v>7800</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2912,9 +2909,6 @@
       <c r="B3">
         <v>5700</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -2924,7 +2918,7 @@
         <v>4000</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2935,7 +2929,7 @@
         <v>1500</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2946,7 +2940,7 @@
         <v>2000</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2957,7 +2951,7 @@
         <v>4100</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2968,7 +2962,7 @@
         <v>1900</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2979,7 +2973,7 @@
         <v>3500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2990,7 +2984,7 @@
         <v>2000</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3001,7 +2995,7 @@
         <v>500</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3019,6 +3013,9 @@
       <c r="B13">
         <v>2700</v>
       </c>
+      <c r="C13">
+        <v>45</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3028,7 +3025,7 @@
         <v>1600</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,7 +3116,7 @@
         <v>5100</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3129,9 +3126,6 @@
       <c r="B3">
         <v>4600</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -3141,7 +3135,7 @@
         <v>2700</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,7 +3146,7 @@
         <v>1500</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,7 +3157,7 @@
         <v>2100</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,7 +3168,7 @@
         <v>3000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,7 +3179,7 @@
         <v>2200</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,7 +3190,7 @@
         <v>3300</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,7 +3201,7 @@
         <v>2300</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,7 +3212,7 @@
         <v>600</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,6 +3230,9 @@
       <c r="B13">
         <v>3200</v>
       </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3245,7 +3242,7 @@
         <v>1600</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,7 +3333,7 @@
         <v>5200</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3346,9 +3343,6 @@
       <c r="B3">
         <v>4700</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -3358,7 +3352,7 @@
         <v>2700</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3369,7 +3363,7 @@
         <v>1600</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3380,7 +3374,7 @@
         <v>2100</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3391,7 +3385,7 @@
         <v>3000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3402,7 +3396,7 @@
         <v>2200</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,7 +3407,7 @@
         <v>3300</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,7 +3418,7 @@
         <v>2300</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3435,7 +3429,7 @@
         <v>600</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,6 +3447,9 @@
       <c r="B13">
         <v>4200</v>
       </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3462,7 +3459,7 @@
         <v>1650</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,7 +3550,7 @@
         <v>10500</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,9 +3560,6 @@
       <c r="B3">
         <v>7200</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -3575,7 +3569,7 @@
         <v>4300</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,7 +3580,7 @@
         <v>1800</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,7 +3591,7 @@
         <v>2100</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,7 +3602,7 @@
         <v>4800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,7 +3613,7 @@
         <v>2400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,7 +3624,7 @@
         <v>3500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,7 +3635,7 @@
         <v>2500</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,7 +3646,7 @@
         <v>600</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3670,6 +3664,9 @@
       <c r="B13">
         <v>4200</v>
       </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3679,7 +3676,7 @@
         <v>1700</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3770,7 +3767,7 @@
         <v>12200</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,9 +3777,6 @@
       <c r="B3">
         <v>8500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -3792,7 +3786,7 @@
         <v>4600</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3803,7 +3797,7 @@
         <v>1900</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3814,7 +3808,7 @@
         <v>2200</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3825,7 +3819,7 @@
         <v>4800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3836,7 +3830,7 @@
         <v>2400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -3847,7 +3841,7 @@
         <v>3500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3858,7 +3852,7 @@
         <v>2500</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3869,7 +3863,7 @@
         <v>600</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3887,6 +3881,9 @@
       <c r="B13">
         <v>4200</v>
       </c>
+      <c r="C13">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3896,7 +3893,7 @@
         <v>1700</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3987,7 +3984,7 @@
         <v>7600</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3997,9 +3994,6 @@
       <c r="B3">
         <v>5500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4009,7 +4003,7 @@
         <v>5100</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4020,7 +4014,7 @@
         <v>1900</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4031,7 +4025,7 @@
         <v>2400</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4042,7 +4036,7 @@
         <v>5500</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4053,7 +4047,7 @@
         <v>2500</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4064,7 +4058,7 @@
         <v>3600</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4075,7 +4069,7 @@
         <v>2600</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4086,7 +4080,7 @@
         <v>800</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4113,7 +4107,7 @@
         <v>2400</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,7 +4198,7 @@
         <v>9600</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4214,9 +4208,6 @@
       <c r="B3">
         <v>6500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4226,7 +4217,7 @@
         <v>5200</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,7 +4228,7 @@
         <v>2100</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4248,7 +4239,7 @@
         <v>2400</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,7 +4250,7 @@
         <v>5600</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4270,7 +4261,7 @@
         <v>2500</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4281,7 +4272,7 @@
         <v>3800</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,7 +4283,7 @@
         <v>2600</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4303,7 +4294,7 @@
         <v>800</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,7 +4321,7 @@
         <v>2400</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4421,7 +4412,7 @@
         <v>13900</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,9 +4422,6 @@
       <c r="B3">
         <v>8500</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4443,7 +4431,7 @@
         <v>6500</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4454,7 +4442,7 @@
         <v>2100</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4465,7 +4453,7 @@
         <v>2400</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4476,7 +4464,7 @@
         <v>5800</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4487,7 +4475,7 @@
         <v>2800</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4498,7 +4486,7 @@
         <v>4000</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4509,7 +4497,7 @@
         <v>3500</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4520,7 +4508,7 @@
         <v>800</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4547,7 +4535,7 @@
         <v>3000</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4638,7 +4626,7 @@
         <v>15500</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,7 +4637,7 @@
         <v>10500</v>
       </c>
       <c r="C3">
-        <v>370</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4660,7 +4648,7 @@
         <v>6500</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,7 +4659,7 @@
         <v>2200</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,7 +4670,7 @@
         <v>2500</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,7 +4681,7 @@
         <v>6000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4704,7 +4692,7 @@
         <v>2800</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,7 +4703,7 @@
         <v>4300</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,7 +4714,7 @@
         <v>3500</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4737,7 +4725,7 @@
         <v>800</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -4764,7 +4752,7 @@
         <v>3200</v>
       </c>
       <c r="C14">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,7 +4900,7 @@
         <v>10500</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4922,9 +4910,6 @@
       <c r="B3">
         <v>8000</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -4934,7 +4919,7 @@
         <v>5200</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,7 +4941,7 @@
         <v>2800</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,7 +4952,7 @@
         <v>7000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4963,7 @@
         <v>3400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,7 +4974,7 @@
         <v>4500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,7 +5007,7 @@
         <v>3000</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,7 +5098,7 @@
         <v>11500</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5123,9 +5108,6 @@
       <c r="B3">
         <v>9000</v>
       </c>
-      <c r="C3">
-        <v>370</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -5135,7 +5117,7 @@
         <v>8000</v>
       </c>
       <c r="C4">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,7 +5139,7 @@
         <v>2800</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,7 +5150,7 @@
         <v>7000</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,7 +5161,7 @@
         <v>3400</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,7 +5172,7 @@
         <v>4500</v>
       </c>
       <c r="C9">
-        <v>95</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5223,7 +5205,7 @@
         <v>3000</v>
       </c>
       <c r="C12">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -5314,7 +5296,7 @@
         <v>16300</v>
       </c>
       <c r="C2">
-        <v>370</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5325,7 +5307,7 @@
         <v>7500</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5347,7 +5329,7 @@
         <v>2800</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5358,7 +5340,7 @@
         <v>7000</v>
       </c>
       <c r="C6">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5369,7 +5351,7 @@
         <v>3800</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -5380,7 +5362,7 @@
         <v>5300</v>
       </c>
       <c r="C8">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5413,7 +5395,7 @@
         <v>3400</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
